--- a/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
+++ b/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ttami001/Documents/forked_tbrs_opensource/trbs/src/vlinder/data/refugee/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/vlinder/trbs/src/vlinder/data/Refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1FCBF3-1EAE-0543-B25E-9A26D4D02AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0A7D9D-83E6-C446-A030-CB48B0018DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="-21280" windowWidth="31660" windowHeight="15880" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
+    <workbookView xWindow="5520" yWindow="760" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
   <sheets>
     <sheet name="configurations" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,10 @@
     <sheet name="scenario_weights" sheetId="9" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">dependencies!$A$1:$H$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">dependencies!$A$1:$H$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">fixed_inputs!$A$1:$B$46</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="299">
   <si>
     <t>configuration</t>
   </si>
@@ -82,9 +82,6 @@
     <t>end</t>
   </si>
   <si>
-    <t>threshold</t>
-  </si>
-  <si>
     <t>internal_variable_input</t>
   </si>
   <si>
@@ -112,24 +109,9 @@
     <t>operator</t>
   </si>
   <si>
-    <t>maximum_effect</t>
-  </si>
-  <si>
-    <t>accessibility</t>
-  </si>
-  <si>
-    <t>probability_of_success</t>
-  </si>
-  <si>
-    <t>saturation_point</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
-    <t>use_theme_weights</t>
-  </si>
-  <si>
     <t>Quality of life Ukrainians</t>
   </si>
   <si>
@@ -553,9 +535,6 @@
     <t>Base case</t>
   </si>
   <si>
-    <t>squeezed *</t>
-  </si>
-  <si>
     <t>+</t>
   </si>
   <si>
@@ -773,13 +752,208 @@
   </si>
   <si>
     <t>EN</t>
+  </si>
+  <si>
+    <t>TECU_me</t>
+  </si>
+  <si>
+    <t>TECU_acc</t>
+  </si>
+  <si>
+    <t>TECU_pos</t>
+  </si>
+  <si>
+    <t>TECU_sp</t>
+  </si>
+  <si>
+    <t>TECU_1</t>
+  </si>
+  <si>
+    <t>TECU_2</t>
+  </si>
+  <si>
+    <t>TECU_3</t>
+  </si>
+  <si>
+    <t>TECU_4</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>LAUS_me</t>
+  </si>
+  <si>
+    <t>LAUS_acc</t>
+  </si>
+  <si>
+    <t>LAUS_pos</t>
+  </si>
+  <si>
+    <t>LAUS_sp</t>
+  </si>
+  <si>
+    <t>LAUS_1</t>
+  </si>
+  <si>
+    <t>LAUS_2</t>
+  </si>
+  <si>
+    <t>LAUS_3</t>
+  </si>
+  <si>
+    <t>LAUS_4</t>
+  </si>
+  <si>
+    <t>LAUI_me</t>
+  </si>
+  <si>
+    <t>LAUI_acc</t>
+  </si>
+  <si>
+    <t>LAUI_pos</t>
+  </si>
+  <si>
+    <t>LAUI_sp</t>
+  </si>
+  <si>
+    <t>LAUI_1</t>
+  </si>
+  <si>
+    <t>LAUI_2</t>
+  </si>
+  <si>
+    <t>LAUI_3</t>
+  </si>
+  <si>
+    <t>LAUI_4</t>
+  </si>
+  <si>
+    <t>URUE_me</t>
+  </si>
+  <si>
+    <t>URUE_acc</t>
+  </si>
+  <si>
+    <t>URUE_pos</t>
+  </si>
+  <si>
+    <t>URUE_sp</t>
+  </si>
+  <si>
+    <t>URUE_1</t>
+  </si>
+  <si>
+    <t>URUE_2</t>
+  </si>
+  <si>
+    <t>URUE_3</t>
+  </si>
+  <si>
+    <t>URUE_4</t>
+  </si>
+  <si>
+    <t>SCUS_me</t>
+  </si>
+  <si>
+    <t>SCUS_acc</t>
+  </si>
+  <si>
+    <t>SCUS_pos</t>
+  </si>
+  <si>
+    <t>SCUS_sp</t>
+  </si>
+  <si>
+    <t>SCUS_1</t>
+  </si>
+  <si>
+    <t>SCUS_2</t>
+  </si>
+  <si>
+    <t>SCUS_3</t>
+  </si>
+  <si>
+    <t>SCUS_4</t>
+  </si>
+  <si>
+    <t>SCUT_me</t>
+  </si>
+  <si>
+    <t>SCUT_acc</t>
+  </si>
+  <si>
+    <t>SCUT_pos</t>
+  </si>
+  <si>
+    <t>SCUT_sp</t>
+  </si>
+  <si>
+    <t>SCUT_1</t>
+  </si>
+  <si>
+    <t>SCUT_2</t>
+  </si>
+  <si>
+    <t>SCUT_3</t>
+  </si>
+  <si>
+    <t>SCUT_4</t>
+  </si>
+  <si>
+    <t>HUSA_me</t>
+  </si>
+  <si>
+    <t>HUSA_acc</t>
+  </si>
+  <si>
+    <t>HUSA_pos</t>
+  </si>
+  <si>
+    <t>HUSA_sp</t>
+  </si>
+  <si>
+    <t>HUSA_1</t>
+  </si>
+  <si>
+    <t>HUSA_2</t>
+  </si>
+  <si>
+    <t>HUSA_3</t>
+  </si>
+  <si>
+    <t>HUSA_4</t>
+  </si>
+  <si>
+    <t>SPUAT_me</t>
+  </si>
+  <si>
+    <t>SPUAT_acc</t>
+  </si>
+  <si>
+    <t>SPUAT_pos</t>
+  </si>
+  <si>
+    <t>SPUAT_sp</t>
+  </si>
+  <si>
+    <t>SPUAT_1</t>
+  </si>
+  <si>
+    <t>SPUAT_2</t>
+  </si>
+  <si>
+    <t>SPUAT_3</t>
+  </si>
+  <si>
+    <t>SPUAT_4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -809,6 +983,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -869,7 +1056,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -887,6 +1074,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1213,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323C0127-B98F-8F4A-8B9E-DB2076867E31}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -1228,19 +1416,11 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>240</v>
+      <c r="A2" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1261,12 +1441,12 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1274,7 +1454,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1282,7 +1462,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1290,7 +1470,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1298,7 +1478,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1306,7 +1486,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1314,7 +1494,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1332,15 +1512,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1348,7 +1528,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1356,7 +1536,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1370,7 +1550,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CE72EE-56C9-CF45-9BB4-E3A3014AFA69}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="163.5" style="6" bestFit="1" customWidth="1"/>
@@ -1379,7 +1559,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -1387,238 +1567,238 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B21" s="7"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B22" s="7"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1809,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A4C952-3079-8241-9F47-5217040C7CD4}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="63" style="6" customWidth="1"/>
@@ -1638,7 +1818,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
@@ -1646,10 +1826,10 @@
     </row>
     <row r="2" spans="1:2" ht="204" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1662,14 +1842,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F27D205-AE79-E542-BA48-2D4707481E26}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1694,16 +1874,13 @@
       <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1724,12 +1901,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1750,12 +1927,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1776,12 +1953,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1802,12 +1979,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1828,12 +2005,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1854,12 +2031,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1899,10 +2076,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1910,10 +2087,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1921,10 +2098,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1932,10 +2109,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>3234502</v>
@@ -1943,10 +2120,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1954,10 +2131,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>3234502</v>
@@ -1965,10 +2142,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>3234502</v>
@@ -1976,10 +2153,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1987,10 +2164,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>3234502</v>
@@ -1998,10 +2175,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2009,10 +2186,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2020,10 +2197,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>3881402.4</v>
@@ -2031,10 +2208,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>2587601.6</v>
@@ -2042,10 +2219,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2053,10 +2230,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2064,10 +2241,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2075,10 +2252,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1293800.8</v>
@@ -2086,10 +2263,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>1293800.8</v>
@@ -2097,10 +2274,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1293800.8</v>
@@ -2108,10 +2285,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>1293800.8</v>
@@ -2119,10 +2296,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>1293800.8</v>
@@ -2130,10 +2307,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2141,10 +2318,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C23">
         <v>2587601.6</v>
@@ -2152,10 +2329,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>3881402.4</v>
@@ -2163,10 +2340,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2174,10 +2351,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2199,10 +2376,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -2210,10 +2387,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C2">
         <v>2587601.6</v>
@@ -2221,10 +2398,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>2587601.6</v>
@@ -2232,10 +2409,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>5175203.3470000001</v>
@@ -2243,10 +2420,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C5">
         <v>0.7</v>
@@ -2254,10 +2431,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>0.7</v>
@@ -2265,10 +2442,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>0.7</v>
@@ -2276,10 +2453,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>36972</v>
@@ -2287,10 +2464,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>21384</v>
@@ -2298,10 +2475,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>27084</v>
@@ -2309,10 +2486,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>26796</v>
@@ -2320,10 +2497,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C12">
         <v>43512</v>
@@ -2331,10 +2508,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C13">
         <v>25332</v>
@@ -2342,10 +2519,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C14">
         <v>34872</v>
@@ -2353,10 +2530,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C15">
         <v>30492</v>
@@ -2364,10 +2541,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>50052</v>
@@ -2375,10 +2552,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>34332</v>
@@ -2386,10 +2563,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>40776</v>
@@ -2397,10 +2574,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>34080</v>
@@ -2413,7 +2590,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED761DDB-51CF-394F-9D46-C056F7FA6C46}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="75" bestFit="1" customWidth="1"/>
@@ -2421,7 +2598,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2429,7 +2606,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>0.81</v>
@@ -2437,7 +2614,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>0.81</v>
@@ -2445,7 +2622,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>0.37</v>
@@ -2453,7 +2630,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>0.01</v>
@@ -2461,7 +2638,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3">
         <v>0.26600000000000001</v>
@@ -2469,7 +2646,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>0.26600000000000001</v>
@@ -2477,7 +2654,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>0.26600000000000001</v>
@@ -2485,7 +2662,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <v>1.1200000000000001</v>
@@ -2493,7 +2670,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B10">
         <v>0.15490000000000001</v>
@@ -2501,7 +2678,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <v>0.22900000000000001</v>
@@ -2509,7 +2686,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>2.1999999999999999E-2</v>
@@ -2517,7 +2694,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B13" s="3">
         <v>7.3000000000000001E-3</v>
@@ -2525,7 +2702,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3">
         <v>7.3000000000000001E-3</v>
@@ -2533,7 +2710,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B15">
         <v>0.26</v>
@@ -2541,7 +2718,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>0.26</v>
@@ -2549,7 +2726,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B17">
         <v>0.28999999999999998</v>
@@ -2557,7 +2734,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B18">
         <v>0.28999999999999998</v>
@@ -2565,7 +2742,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B19">
         <v>0.28999999999999998</v>
@@ -2573,7 +2750,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B20">
         <v>4.1000000000000003E-3</v>
@@ -2581,7 +2758,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B21">
         <v>0.82</v>
@@ -2589,7 +2766,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>0.82</v>
@@ -2597,7 +2774,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B23">
         <v>9.1200000000000003E-2</v>
@@ -2605,7 +2782,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -2613,7 +2790,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B25">
         <v>0.26700000000000002</v>
@@ -2621,7 +2798,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B26">
         <v>0.158</v>
@@ -2629,7 +2806,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B27">
         <v>0.26</v>
@@ -2637,7 +2814,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B28">
         <v>0.36299999999999999</v>
@@ -2645,7 +2822,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B29">
         <v>0.39100000000000001</v>
@@ -2653,7 +2830,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B30">
         <v>0.20899999999999999</v>
@@ -2661,7 +2838,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B31">
         <v>0.46</v>
@@ -2669,7 +2846,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B32">
         <v>0.46</v>
@@ -2677,7 +2854,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B33">
         <v>0.46</v>
@@ -2685,7 +2862,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B34" s="2">
         <v>1</v>
@@ -2693,7 +2870,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B35">
         <v>-0.05</v>
@@ -2701,7 +2878,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B36">
         <v>-0.05</v>
@@ -2709,7 +2886,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B37">
         <v>20700</v>
@@ -2717,7 +2894,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B38">
         <v>6.0999999999999999E-2</v>
@@ -2725,7 +2902,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B39">
         <v>0.19700000000000001</v>
@@ -2733,7 +2910,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B40">
         <v>0.74199999999999999</v>
@@ -2741,7 +2918,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B41">
         <v>1532</v>
@@ -2749,7 +2926,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B42">
         <v>24000</v>
@@ -2757,7 +2934,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B43">
         <v>3105</v>
@@ -2765,7 +2942,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B44">
         <v>3120</v>
@@ -2773,7 +2950,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B45">
         <v>3120</v>
@@ -2781,10 +2958,266 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B46">
         <v>14352</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>236</v>
+      </c>
+      <c r="B49">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B50">
+        <v>13774010.720000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>244</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>245</v>
+      </c>
+      <c r="B53">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54">
+        <v>1630189.054</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>251</v>
+      </c>
+      <c r="B55">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>252</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>253</v>
+      </c>
+      <c r="B57">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>254</v>
+      </c>
+      <c r="B58">
+        <v>7946938.7560000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>259</v>
+      </c>
+      <c r="B59">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>262</v>
+      </c>
+      <c r="B62">
+        <v>8150945.2719999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>267</v>
+      </c>
+      <c r="B63">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>268</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66">
+        <v>1630189.054</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>276</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>277</v>
+      </c>
+      <c r="B69">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>278</v>
+      </c>
+      <c r="B70">
+        <v>15216753.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>283</v>
+      </c>
+      <c r="B71">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>284</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>285</v>
+      </c>
+      <c r="B73">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>286</v>
+      </c>
+      <c r="B74">
+        <v>1630189.054</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75">
+        <v>0.53700000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>292</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>293</v>
+      </c>
+      <c r="B77">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>294</v>
+      </c>
+      <c r="B78">
+        <v>15216753.91</v>
       </c>
     </row>
   </sheetData>
@@ -2798,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45498073-CC56-2D41-B5D6-3D03F1233978}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
@@ -2810,1464 +3243,1828 @@
     <col min="8" max="8" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>237</v>
       </c>
       <c r="D2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" t="s">
+        <v>252</v>
+      </c>
+      <c r="D26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>167</v>
       </c>
-      <c r="E2">
-        <v>0.47</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0.71</v>
-      </c>
-      <c r="H2">
-        <v>13774010.720000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15">
-        <v>0.42</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>0.7</v>
-      </c>
-      <c r="H15">
-        <v>1630189.054</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16">
-        <v>0.65</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0.7</v>
-      </c>
-      <c r="H16">
-        <v>7946938.7560000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20">
-        <v>0.68</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>0.6</v>
-      </c>
-      <c r="H20">
-        <v>8150945.2719999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>134</v>
-      </c>
       <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
       </c>
       <c r="D30" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
+        <v>263</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>264</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>265</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>261</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>266</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
+        <v>169</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>41</v>
+        <v>101</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>120</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>118</v>
       </c>
-      <c r="C49" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="B70" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" t="s">
+        <v>86</v>
+      </c>
+      <c r="D70" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>122</v>
+      </c>
+      <c r="B72" t="s">
+        <v>116</v>
+      </c>
+      <c r="C72" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" t="s">
+        <v>118</v>
+      </c>
+      <c r="C73" t="s">
+        <v>119</v>
+      </c>
+      <c r="D73" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" t="s">
         <v>121</v>
       </c>
-      <c r="B50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="D74" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" t="s">
         <v>122</v>
       </c>
-      <c r="B52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D52" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>123</v>
-      </c>
-      <c r="B53" t="s">
-        <v>120</v>
-      </c>
-      <c r="C53" t="s">
-        <v>91</v>
-      </c>
-      <c r="D53" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" t="s">
-        <v>117</v>
-      </c>
-      <c r="C55" t="s">
-        <v>93</v>
-      </c>
-      <c r="D55" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>128</v>
-      </c>
-      <c r="B56" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" t="s">
-        <v>125</v>
-      </c>
-      <c r="D57" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" t="s">
-        <v>126</v>
-      </c>
-      <c r="C58" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B59" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>138</v>
-      </c>
-      <c r="B60" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" t="s">
-        <v>51</v>
-      </c>
-      <c r="D60" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" t="s">
-        <v>53</v>
-      </c>
-      <c r="D61" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" t="s">
-        <v>43</v>
-      </c>
-      <c r="D62" t="s">
-        <v>167</v>
-      </c>
-      <c r="E62">
-        <v>0.12</v>
-      </c>
-      <c r="F62">
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B76" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" t="s">
+        <v>37</v>
+      </c>
+      <c r="C78" t="s">
+        <v>270</v>
+      </c>
+      <c r="D78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79">
         <v>1</v>
       </c>
-      <c r="G62">
-        <v>0.7</v>
-      </c>
-      <c r="H62">
-        <v>1630189.054</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63">
-        <v>1.4E-2</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
-        <v>0.6</v>
-      </c>
-      <c r="H63">
-        <v>15216753.91</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" t="s">
-        <v>129</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" t="s">
-        <v>131</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" t="s">
-        <v>74</v>
-      </c>
-      <c r="D67" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>135</v>
-      </c>
-      <c r="B68" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" t="s">
-        <v>62</v>
-      </c>
-      <c r="D68" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" t="s">
-        <v>134</v>
-      </c>
-      <c r="C69" t="s">
-        <v>63</v>
-      </c>
-      <c r="D69" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" t="s">
-        <v>135</v>
-      </c>
-      <c r="C70" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>151</v>
-      </c>
-      <c r="B71" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" t="s">
-        <v>65</v>
-      </c>
-      <c r="D71" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>158</v>
-      </c>
-      <c r="B72" t="s">
-        <v>135</v>
-      </c>
-      <c r="C72" t="s">
-        <v>66</v>
-      </c>
-      <c r="D72" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>137</v>
-      </c>
-      <c r="B73" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" t="s">
-        <v>72</v>
-      </c>
-      <c r="D73" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>141</v>
-      </c>
-      <c r="B74" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" t="s">
-        <v>137</v>
-      </c>
-      <c r="D74" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>139</v>
-      </c>
-      <c r="B75" t="s">
-        <v>43</v>
-      </c>
-      <c r="D75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E75">
-        <v>0.22</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75">
-        <v>0.7</v>
-      </c>
-      <c r="H75">
-        <v>1630189.054</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>142</v>
-      </c>
-      <c r="B76" t="s">
-        <v>44</v>
-      </c>
-      <c r="D76" t="s">
-        <v>167</v>
-      </c>
-      <c r="E76">
-        <v>0.53700000000000003</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
-        <v>0.6</v>
-      </c>
-      <c r="H76">
-        <v>15216753.91</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>140</v>
-      </c>
-      <c r="B77" t="s">
-        <v>134</v>
-      </c>
-      <c r="C77" t="s">
-        <v>60</v>
-      </c>
-      <c r="D77" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" t="s">
-        <v>133</v>
-      </c>
-      <c r="C78" t="s">
-        <v>61</v>
-      </c>
-      <c r="D78" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>157</v>
-      </c>
-      <c r="B79" t="s">
-        <v>138</v>
-      </c>
-      <c r="C79" t="s">
-        <v>67</v>
-      </c>
       <c r="D79" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>150</v>
-      </c>
-      <c r="B80" t="s">
-        <v>30</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>272</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>145</v>
-      </c>
-      <c r="B81" t="s">
-        <v>139</v>
+      <c r="A81" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>269</v>
       </c>
       <c r="D81" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>146</v>
-      </c>
-      <c r="B82" t="s">
-        <v>140</v>
+        <v>123</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="D82" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>147</v>
+      <c r="A83" s="11" t="s">
+        <v>279</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
-        <v>69</v>
+        <v>278</v>
       </c>
       <c r="D83" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>148</v>
-      </c>
-      <c r="B84" t="s">
-        <v>132</v>
-      </c>
-      <c r="C84" t="s">
-        <v>75</v>
+      <c r="A84" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>144</v>
-      </c>
-      <c r="B85" t="s">
-        <v>142</v>
+      <c r="A85" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>280</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="D85" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>26</v>
-      </c>
-      <c r="B86" t="s">
-        <v>143</v>
+      <c r="A86" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>281</v>
       </c>
       <c r="C86" t="s">
-        <v>144</v>
+        <v>277</v>
       </c>
       <c r="D86" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>26</v>
-      </c>
-      <c r="B87" t="s">
-        <v>145</v>
+        <v>124</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>282</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="D87" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="D88" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="C89" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="D89" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
-      </c>
-      <c r="C90" t="s">
-        <v>77</v>
+        <v>125</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
         <v>68</v>
       </c>
       <c r="D91" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="D93" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="B94" t="s">
-        <v>156</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
+        <v>129</v>
+      </c>
+      <c r="C94" t="s">
+        <v>58</v>
       </c>
       <c r="D94" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D95" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B96" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D96" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="B97" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="D97" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98" t="s">
+        <v>131</v>
+      </c>
+      <c r="D98" t="s">
         <v>161</v>
       </c>
-      <c r="C98" t="s">
-        <v>162</v>
-      </c>
-      <c r="D98" t="s">
-        <v>168</v>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" t="s">
+        <v>286</v>
+      </c>
+      <c r="D99" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>288</v>
+      </c>
+      <c r="B100" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>289</v>
+      </c>
+      <c r="B101" t="s">
+        <v>288</v>
+      </c>
+      <c r="C101" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>290</v>
+      </c>
+      <c r="B102" t="s">
+        <v>289</v>
+      </c>
+      <c r="C102" t="s">
+        <v>285</v>
+      </c>
+      <c r="D102" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>133</v>
+      </c>
+      <c r="B103" t="s">
+        <v>290</v>
+      </c>
+      <c r="C103" t="s">
+        <v>283</v>
+      </c>
+      <c r="D103" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>295</v>
+      </c>
+      <c r="B104" t="s">
+        <v>38</v>
+      </c>
+      <c r="C104" t="s">
+        <v>294</v>
+      </c>
+      <c r="D104" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>296</v>
+      </c>
+      <c r="B105" t="s">
+        <v>295</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>297</v>
+      </c>
+      <c r="B106" t="s">
+        <v>296</v>
+      </c>
+      <c r="C106" t="s">
+        <v>292</v>
+      </c>
+      <c r="D106" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>298</v>
+      </c>
+      <c r="B107" t="s">
+        <v>297</v>
+      </c>
+      <c r="C107" t="s">
+        <v>293</v>
+      </c>
+      <c r="D107" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" t="s">
+        <v>298</v>
+      </c>
+      <c r="C108" t="s">
+        <v>291</v>
+      </c>
+      <c r="D108" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>134</v>
+      </c>
+      <c r="B109" t="s">
+        <v>128</v>
+      </c>
+      <c r="C109" t="s">
+        <v>54</v>
+      </c>
+      <c r="D109" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>143</v>
+      </c>
+      <c r="B110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s">
+        <v>55</v>
+      </c>
+      <c r="D110" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>151</v>
+      </c>
+      <c r="B111" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>144</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>139</v>
+      </c>
+      <c r="B113" t="s">
+        <v>133</v>
+      </c>
+      <c r="C113" t="s">
+        <v>50</v>
+      </c>
+      <c r="D113" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>140</v>
+      </c>
+      <c r="B114" t="s">
+        <v>134</v>
+      </c>
+      <c r="C114" t="s">
+        <v>72</v>
+      </c>
+      <c r="D114" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>141</v>
+      </c>
+      <c r="B115" t="s">
+        <v>135</v>
+      </c>
+      <c r="C115" t="s">
+        <v>63</v>
+      </c>
+      <c r="D115" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>142</v>
+      </c>
+      <c r="B116" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" t="s">
+        <v>69</v>
+      </c>
+      <c r="D116" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>138</v>
+      </c>
+      <c r="B117" t="s">
+        <v>136</v>
+      </c>
+      <c r="C117" t="s">
+        <v>70</v>
+      </c>
+      <c r="D117" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>20</v>
+      </c>
+      <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
+        <v>138</v>
+      </c>
+      <c r="D118" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>20</v>
+      </c>
+      <c r="B119" t="s">
+        <v>139</v>
+      </c>
+      <c r="C119" t="s">
+        <v>140</v>
+      </c>
+      <c r="D119" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>20</v>
+      </c>
+      <c r="B120" t="s">
+        <v>141</v>
+      </c>
+      <c r="C120" t="s">
+        <v>142</v>
+      </c>
+      <c r="D120" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>148</v>
+      </c>
+      <c r="B121" t="s">
+        <v>143</v>
+      </c>
+      <c r="C121" t="s">
+        <v>73</v>
+      </c>
+      <c r="D121" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>149</v>
+      </c>
+      <c r="B122" t="s">
+        <v>144</v>
+      </c>
+      <c r="C122" t="s">
+        <v>71</v>
+      </c>
+      <c r="D122" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>150</v>
+      </c>
+      <c r="B123" t="s">
+        <v>145</v>
+      </c>
+      <c r="C123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D123" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124" t="s">
+        <v>146</v>
+      </c>
+      <c r="C124" t="s">
+        <v>147</v>
+      </c>
+      <c r="D124" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125" t="s">
+        <v>148</v>
+      </c>
+      <c r="C125" t="s">
+        <v>149</v>
+      </c>
+      <c r="D125" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>21</v>
+      </c>
+      <c r="B126" t="s">
+        <v>150</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>155</v>
+      </c>
+      <c r="B127" t="s">
+        <v>151</v>
+      </c>
+      <c r="C127" t="s">
+        <v>74</v>
+      </c>
+      <c r="D127" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>156</v>
+      </c>
+      <c r="B128" t="s">
+        <v>152</v>
+      </c>
+      <c r="C128" t="s">
+        <v>64</v>
+      </c>
+      <c r="D128" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" t="s">
+        <v>154</v>
+      </c>
+      <c r="D129" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" t="s">
+        <v>155</v>
+      </c>
+      <c r="C130" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H98" xr:uid="{45498073-CC56-2D41-B5D6-3D03F1233978}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4282,12 +5079,12 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -4295,7 +5092,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>1</v>

--- a/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
+++ b/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/vlinder/trbs/src/vlinder/data/Refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0A7D9D-83E6-C446-A030-CB48B0018DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB166531-5897-6F4F-B210-BC8C38A7EA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="760" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
@@ -1894,12 +1894,6 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1920,12 +1914,6 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1946,12 +1934,6 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1972,12 +1954,6 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1998,12 +1974,6 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2024,12 +1994,6 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2049,12 +2013,6 @@
       </c>
       <c r="F8">
         <v>1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>50000000</v>
       </c>
     </row>
   </sheetData>

--- a/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
+++ b/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/vlinder/trbs/src/vlinder/data/Refugee/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mverdaasdo001/Documents/Aangepast_report/trbs/src/vlinder/data/Refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB166531-5897-6F4F-B210-BC8C38A7EA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327F8EEF-D7B7-6C4E-BDD4-47E2EDBE3C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="760" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
+    <workbookView xWindow="5520" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
   <sheets>
     <sheet name="configurations" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="312">
   <si>
     <t>configuration</t>
   </si>
@@ -947,6 +947,45 @@
   </si>
   <si>
     <t>SPUAT_4</t>
+  </si>
+  <si>
+    <t>Optimize_DMO_name</t>
+  </si>
+  <si>
+    <t>Optimized_DMO</t>
+  </si>
+  <si>
+    <t>report_title_page</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>report_strategic_challenge</t>
+  </si>
+  <si>
+    <t>report_key_outputs_theme</t>
+  </si>
+  <si>
+    <t>report_decision_makers_options</t>
+  </si>
+  <si>
+    <t>report_scenarios</t>
+  </si>
+  <si>
+    <t>report_fixed_inputs</t>
+  </si>
+  <si>
+    <t>report_dependencies</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>report_weighted_appreciations</t>
+  </si>
+  <si>
+    <t>report_add_optimize</t>
   </si>
 </sst>
 </file>
@@ -1077,8 +1116,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DA9729B0-9B76-C84C-86B6-0F66A13A4DF8}"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1105,7 +1144,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1401,10 +1440,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323C0127-B98F-8F4A-8B9E-DB2076867E31}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1421,6 +1461,86 @@
       </c>
       <c r="B2" s="10" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
+++ b/src/vlinder/data/Refugee/xlsx/Refugee.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mverdaasdo001/Documents/Aangepast_report/trbs/src/vlinder/data/Refugee/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/vlinder/trbs-dev/src/vlinder/data/Refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327F8EEF-D7B7-6C4E-BDD4-47E2EDBE3C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9417B70-CC78-1646-B602-CB6F25C3DE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="311">
   <si>
     <t>configuration</t>
   </si>
@@ -983,9 +983,6 @@
   </si>
   <si>
     <t>report_weighted_appreciations</t>
-  </si>
-  <si>
-    <t>report_add_optimize</t>
   </si>
 </sst>
 </file>
@@ -1116,8 +1113,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DA9729B0-9B76-C84C-86B6-0F66A13A4DF8}"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1144,7 +1141,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1440,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323C0127-B98F-8F4A-8B9E-DB2076867E31}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
@@ -1533,14 +1530,6 @@
       </c>
       <c r="B11" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>311</v>
-      </c>
-      <c r="B12" t="s">
-        <v>309</v>
       </c>
     </row>
   </sheetData>
